--- a/artfynd/A 24907-2024 artfynd.xlsx
+++ b/artfynd/A 24907-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>70327981</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375563.0138475301</v>
+        <v>375563</v>
       </c>
       <c r="R2" t="n">
-        <v>6772366.197457335</v>
+        <v>6772366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2017-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 24907-2024 artfynd.xlsx
+++ b/artfynd/A 24907-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>70327981</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
